--- a/plugins/consulting-office/skills/new-client/assets/00 תיק לקוח.xlsx
+++ b/plugins/consulting-office/skills/new-client/assets/00 תיק לקוח.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,12 @@
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6670"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F5E63"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -103,26 +109,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="009C2B1E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE3E0"/>
+          <bgColor rgb="00FBE3E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="008A939B"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -613,11 +648,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -637,81 +675,318 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>משימות פתוחות</t>
-        </is>
-      </c>
-      <c r="B4" s="4">
+          <t>התקדמות במשימות</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>אחוז השלמה</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>IF(B8=0,"",B6/B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>הושלמו</t>
+        </is>
+      </c>
+      <c r="B6" s="6">
+        <f>COUNTIFS(tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוצעה")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>נשארו</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>B8-B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>סך הכל משימות</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <f>COUNTIFS(tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"&lt;&gt;")-COUNTIFS(tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוטלה")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>מתוך מה שנשאר: באיחור</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>COUNTIFS(tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"פתוחה",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())+COUNTIFS(tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בטיפול",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>משימות חד-פעמיות, בלי מה שבוטל. משימה שוטפת לא נסגרת, ולכן היא בנפרד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>משימות שוטפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>פעילות</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
+        <f>COUNTIFS(tblTasks[סוג],"שוטפת",tblTasks[סטטוס],"פתוחה")+COUNTIFS(tblTasks[סוג],"שוטפת",tblTasks[סטטוס],"בטיפול")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>בזמן</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <f>B13-B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>באיחור</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>COUNTIFS(tblTasks[סוג],"שוטפת",tblTasks[סטטוס],"פתוחה",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())+COUNTIFS(tblTasks[סוג],"שוטפת",tblTasks[סטטוס],"בטיפול",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>התקדמות לפי צד</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>צד</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>הושלמו</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>נשארו</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>באיחור</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>אחוז השלמה</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>לקוח</t>
+        </is>
+      </c>
+      <c r="B19" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A19,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוצעה")</f>
+        <v/>
+      </c>
+      <c r="C19" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A19,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"&lt;&gt;")-COUNTIFS(tblTasks[צד],$A19,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוטלה")-B19</f>
+        <v/>
+      </c>
+      <c r="D19" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A19,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"פתוחה",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())+COUNTIFS(tblTasks[צד],$A19,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בטיפול",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="E19" s="9">
+        <f>IF(B19+C19=0,"",B19/(B19+C19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>יאן</t>
+        </is>
+      </c>
+      <c r="B20" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A20,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוצעה")</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A20,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"&lt;&gt;")-COUNTIFS(tblTasks[צד],$A20,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוטלה")-B20</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A20,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"פתוחה",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())+COUNTIFS(tblTasks[צד],$A20,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בטיפול",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
+        <f>IF(B20+C20=0,"",B20/(B20+C20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>גורם חוץ</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A21,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוצעה")</f>
+        <v/>
+      </c>
+      <c r="C21" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A21,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"&lt;&gt;")-COUNTIFS(tblTasks[צד],$A21,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בוטלה")-B21</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>COUNTIFS(tblTasks[צד],$A21,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"פתוחה",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())+COUNTIFS(tblTasks[צד],$A21,tblTasks[סוג],"&lt;&gt;שוטפת",tblTasks[סטטוס],"בטיפול",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="E21" s="9">
+        <f>IF(B21+C21=0,"",B21/(B21+C21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>משימות פתוחות (כולל שוטפות)</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
         <f>COUNTIFS(tblTasks[סטטוס],"פתוחה")+COUNTIFS(tblTasks[סטטוס],"בטיפול")</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>משימות באיחור</t>
-        </is>
-      </c>
-      <c r="B5" s="4">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>משימות באיחור (כולל שוטפות)</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
         <f>COUNTIFS(tblTasks[סטטוס],"פתוחה",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())+COUNTIFS(tblTasks[סטטוס],"בטיפול",tblTasks[יעד לטיפול],"&lt;"&amp;TODAY())</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>משימות פתוחות של יאן</t>
         </is>
       </c>
-      <c r="B6" s="4">
+      <c r="B26" s="6">
         <f>COUNTIFS(tblTasks[צד],"יאן",tblTasks[סטטוס],"פתוחה")+COUNTIFS(tblTasks[צד],"יאן",tblTasks[סטטוס],"בטיפול")</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>נושאים פתוחים</t>
         </is>
       </c>
-      <c r="B7" s="4">
+      <c r="B27" s="6">
         <f>COUNTIFS(tblOpen[סטטוס],"פתוח")</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>עקרונות בתוקף</t>
         </is>
       </c>
-      <c r="B8" s="4">
+      <c r="B28" s="6">
         <f>COUNTIFS(tblPrinciples[בתוקף],"כן")</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>פגישה אחרונה</t>
         </is>
       </c>
-      <c r="B9" s="5">
+      <c r="B29" s="10">
         <f>IF(COUNT(tblMeetings[תאריך])=0,"",MAX(tblMeetings[תאריך]))</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>פגישה הבאה</t>
         </is>
       </c>
-      <c r="B10" s="5">
+      <c r="B30" s="10">
         <f>IF(COUNT(tblMeetings[פגישה הבאה])=0,"",MAX(tblMeetings[פגישה הבאה]))</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="000F5E63"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E21">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="000F5E63"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -741,72 +1016,72 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>גרסת תבנית</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>lst_topic</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>lst_side</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>lst_kind</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>lst_freq</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>lst_task_status</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>lst_yesno</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>lst_log_kind</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>lst_open_status</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>lst_goal_status</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>lst_risk_kind</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>lst_severity</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>lst_risk_status</t>
         </is>
@@ -1093,88 +1368,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>מזהה</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>נושא ראשי</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>הנושא לטיפול</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>גורם מטפל</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>צד</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>סוג</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>תדירות</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>יעד לטיפול</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>סטטוס</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>תאריך סגירה</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>פגישת מקור</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>חסוי</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="9" t="n"/>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="13" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:M2000">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>AND(OR($I2="פתוחה",$I2="בטיפול"),ISNUMBER($H2),$H2&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>OR($I2="בוצעה",$I2="בוטלה")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ערך לא ברשימה" error="בחר ערך מהרשימה הנפתחת" type="list">
       <formula1>=lst_topic</formula1>
@@ -1221,50 +1504,50 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>סוג</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>תיאור</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>מי החליט</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>פגישת מקור</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>חסוי</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="8" t="n"/>
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="13" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -1300,44 +1583,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>מזהה</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>עיקרון</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>מאז</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>פגישת מקור</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>בתוקף</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="8" t="n"/>
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1371,50 +1654,50 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>מזהה</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>נושא</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>עלה לראשונה</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>תאריך החלטה צפוי</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>סטטוס</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>פגישת מקור</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="8" t="n"/>
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="13" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1447,44 +1730,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>יעד</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>מדד</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>ערך יעד</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>תאריך יעד</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>סטטוס</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="8" t="n"/>
+      <c r="A2" s="13" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1517,44 +1800,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>חודש</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>מדד</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>ערך</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>יחידה</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>קובץ מקור</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="8" t="n"/>
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1582,44 +1865,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>סוג</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>תיאור</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>חומרה</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>סטטוס</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>פגישת מקור</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="9" t="n"/>
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="14" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1658,44 +1941,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>תאריך</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>נושא</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>משתתפים</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>תיקייה</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>פגישה הבאה</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="8" t="n"/>
+      <c r="A2" s="14" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
